--- a/data/FTA_2023_RawData_Knowledge_Graph.xlsx
+++ b/data/FTA_2023_RawData_Knowledge_Graph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Work\FTA_2023_Knowledge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AAA689-68E3-42A7-9586-DB461A834759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE9E491-6181-4258-BC9E-E08F166DD8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,7 @@
     <sheet name="FTA_Perpose" sheetId="7" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">FTA_Airport_State_Wise!$A$1:$K$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FTA_Count!$A$1:$F$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FTA_Country_Region!$A$1:$B$73</definedName>
   </definedNames>
@@ -2540,7 +2541,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -5358,6 +5359,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E8E685A-51BC-47CC-9B4F-852876B3E36F}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5409,7 +5411,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5422,12 +5424,12 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -5462,7 +5464,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>487</v>
       </c>
@@ -5497,7 +5499,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -5532,7 +5534,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -5567,12 +5569,12 @@
         <v>490</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -5607,7 +5609,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -5642,7 +5644,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>81</v>
       </c>
@@ -5677,7 +5679,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -5712,7 +5714,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -5747,12 +5749,12 @@
         <v>488</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -5787,7 +5789,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>102</v>
       </c>
@@ -5822,7 +5824,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>107</v>
       </c>
@@ -5857,7 +5859,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>112</v>
       </c>
@@ -5892,7 +5894,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>116</v>
       </c>
@@ -5927,7 +5929,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>121</v>
       </c>
@@ -5962,7 +5964,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -5997,7 +5999,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>129</v>
       </c>
@@ -6032,7 +6034,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>134</v>
       </c>
@@ -6067,7 +6069,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>140</v>
       </c>
@@ -6102,7 +6104,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>145</v>
       </c>
@@ -6137,7 +6139,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -6172,7 +6174,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>156</v>
       </c>
@@ -6207,7 +6209,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>161</v>
       </c>
@@ -6242,7 +6244,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>166</v>
       </c>
@@ -6277,7 +6279,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>169</v>
       </c>
@@ -6312,7 +6314,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -6347,7 +6349,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>64</v>
       </c>
@@ -6382,12 +6384,12 @@
         <v>564</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -6422,7 +6424,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>184</v>
       </c>
@@ -6457,7 +6459,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>189</v>
       </c>
@@ -6492,7 +6494,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>192</v>
       </c>
@@ -6527,7 +6529,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>572</v>
       </c>
@@ -6562,7 +6564,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>203</v>
       </c>
@@ -6597,7 +6599,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -6632,7 +6634,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>64</v>
       </c>
@@ -6667,12 +6669,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>216</v>
       </c>
@@ -6707,7 +6709,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>221</v>
       </c>
@@ -6742,7 +6744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>225</v>
       </c>
@@ -6777,7 +6779,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>229</v>
       </c>
@@ -6812,7 +6814,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>232</v>
       </c>
@@ -6847,7 +6849,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>237</v>
       </c>
@@ -6882,7 +6884,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>241</v>
       </c>
@@ -6917,7 +6919,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -6952,7 +6954,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -6987,12 +6989,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>251</v>
       </c>
@@ -7027,7 +7029,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>257</v>
       </c>
@@ -7062,7 +7064,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>262</v>
       </c>
@@ -7097,7 +7099,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>266</v>
       </c>
@@ -7132,7 +7134,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>270</v>
       </c>
@@ -7167,7 +7169,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>274</v>
       </c>
@@ -7202,7 +7204,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>603</v>
       </c>
@@ -7237,7 +7239,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>282</v>
       </c>
@@ -7272,7 +7274,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -7307,7 +7309,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -7342,12 +7344,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>291</v>
       </c>
@@ -7382,7 +7384,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>294</v>
       </c>
@@ -7417,7 +7419,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>299</v>
       </c>
@@ -7452,7 +7454,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>302</v>
       </c>
@@ -7487,7 +7489,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>306</v>
       </c>
@@ -7522,7 +7524,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>310</v>
       </c>
@@ -7592,7 +7594,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>318</v>
       </c>
@@ -7627,7 +7629,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>64</v>
       </c>
@@ -7662,12 +7664,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>326</v>
       </c>
@@ -7702,7 +7704,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>331</v>
       </c>
@@ -7737,7 +7739,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>335</v>
       </c>
@@ -7772,7 +7774,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>338</v>
       </c>
@@ -7807,7 +7809,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>341</v>
       </c>
@@ -7842,7 +7844,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>345</v>
       </c>
@@ -7877,7 +7879,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>351</v>
       </c>
@@ -7912,7 +7914,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>60</v>
       </c>
@@ -7947,7 +7949,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>64</v>
       </c>
@@ -7982,12 +7984,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>362</v>
       </c>
@@ -8022,7 +8024,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>367</v>
       </c>
@@ -8057,7 +8059,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>628</v>
       </c>
@@ -8092,7 +8094,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>60</v>
       </c>
@@ -8127,7 +8129,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>64</v>
       </c>
@@ -8162,12 +8164,12 @@
         <v>505</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>381</v>
       </c>
@@ -8202,7 +8204,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>384</v>
       </c>
@@ -8237,7 +8239,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>60</v>
       </c>
@@ -8272,7 +8274,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>64</v>
       </c>
@@ -8307,7 +8309,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>395</v>
       </c>
@@ -8342,7 +8344,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>399</v>
       </c>
@@ -8378,6 +8380,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K95" xr:uid="{5E8E685A-51BC-47CC-9B4F-852876B3E36F}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Pakistan"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
